--- a/data/trans_orig/P1430-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Habitat-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2012</t>
+          <t>Población con diagnóstico de cirrosis en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13130</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5239</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18966</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>689812</t>
+          <t>690339</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701288</t>
+          <t>701312</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>686882</t>
+          <t>687754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696003</t>
+          <t>696007</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1381553</t>
+          <t>1381657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1395243</t>
+          <t>1395280</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3963</t>
+          <t>3909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15435</t>
+          <t>15397</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>4278</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16449</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10396</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27180</t>
+          <t>25970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002512</t>
+          <t>1002550</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1013984</t>
+          <t>1014038</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012524</t>
+          <t>1012433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1025624</t>
+          <t>1024695</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2019741</t>
+          <t>2020951</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2036525</t>
+          <t>2038068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15109</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>987</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8536</t>
+          <t>9195</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18180</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>742514</t>
+          <t>741456</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755552</t>
+          <t>755445</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768638</t>
+          <t>767979</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776194</t>
+          <t>776187</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1516617</t>
+          <t>1515778</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530623</t>
+          <t>1530470</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>983</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11748</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2080</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12893</t>
+          <t>13188</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>5044</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19846</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>935991</t>
+          <t>934628</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946756</t>
+          <t>946735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,9%</t>
+          <t>99,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1039008</t>
+          <t>1038713</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049821</t>
+          <t>1049884</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1979380</t>
+          <t>1979794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1994681</t>
+          <t>1994596</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38260</t>
+          <t>37453</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13852</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33525</t>
+          <t>32609</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33743</t>
+          <t>33844</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63517</t>
+          <t>63330</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3388519</t>
+          <t>3389326</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3410975</t>
+          <t>3411220</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3521573</t>
+          <t>3522489</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3541246</t>
+          <t>3541217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6918360</t>
+          <t>6918547</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6948134</t>
+          <t>6948033</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cirrosis en 2016</t>
+          <t>Población con diagnóstico de cirrosis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1084</t>
+          <t>1145</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10794</t>
+          <t>10166</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2693,12 +2693,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13413</t>
+          <t>14124</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664006</t>
+          <t>664634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673716</t>
+          <t>673655</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665739</t>
+          <t>665581</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1334226</t>
+          <t>1333515</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1345347</t>
+          <t>1344788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,79%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14359</t>
+          <t>12971</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14305</t>
+          <t>13494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4959</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20099</t>
+          <t>21106</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1008072</t>
+          <t>1009460</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1028608</t>
+          <t>1029419</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041141</t>
+          <t>1041154</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2045245</t>
+          <t>2044238</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2060385</t>
+          <t>2060357</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2091</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14936</t>
+          <t>15953</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>8937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>18172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>744616</t>
+          <t>743599</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757461</t>
+          <t>757018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>777038</t>
+          <t>776074</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1526548</t>
+          <t>1526391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1540603</t>
+          <t>1540553</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3009</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16349</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20651</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921218</t>
+          <t>921662</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934558</t>
+          <t>933822</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033079</t>
+          <t>1033471</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042798</t>
+          <t>1042778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,91%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960695</t>
+          <t>1960431</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975225</t>
+          <t>1975291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14996</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36530</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7269</t>
+          <t>7265</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25495</t>
+          <t>23697</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25979</t>
+          <t>27544</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53836</t>
+          <t>53748</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4135,12 +4135,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3357820</t>
+          <t>3358108</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3379354</t>
+          <t>3379345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3519047</t>
+          <t>3520845</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3537273</t>
+          <t>3537277</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6885056</t>
+          <t>6885144</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6912913</t>
+          <t>6911348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,12 +4248,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1430-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1430-Habitat-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13130</t>
+          <t>13750</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -751,7 +751,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>9371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5239</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18714</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>690339</t>
+          <t>689719</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>701312</t>
+          <t>701269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>687754</t>
+          <t>687679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>696007</t>
+          <t>696004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1381657</t>
+          <t>1381805</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1395280</t>
+          <t>1395253</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15397</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16540</t>
+          <t>17713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1129,7 +1129,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8853</t>
+          <t>10110</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25970</t>
+          <t>26815</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,31%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1002550</t>
+          <t>1003520</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1014038</t>
+          <t>1014420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1012433</t>
+          <t>1011260</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1024695</t>
+          <t>1024662</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2020951</t>
+          <t>2020106</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2038068</t>
+          <t>2036811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17271</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1432,12 +1432,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4230</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>19256</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>741456</t>
+          <t>740352</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>755445</t>
+          <t>755506</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>767979</t>
+          <t>766722</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>776187</t>
+          <t>776188</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1515778</t>
+          <t>1515541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1530470</t>
+          <t>1530567</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>12321</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2017</t>
+          <t>2931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13188</t>
+          <t>13314</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>4958</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19846</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>934628</t>
+          <t>935418</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>946735</t>
+          <t>946754</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,89%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1038713</t>
+          <t>1038587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1049884</t>
+          <t>1048970</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1979794</t>
+          <t>1980562</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1994596</t>
+          <t>1994682</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2103,12 +2103,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15559</t>
+          <t>15755</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37453</t>
+          <t>38256</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2118,12 +2118,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32609</t>
+          <t>33293</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33844</t>
+          <t>34241</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>63330</t>
+          <t>63142</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2188,12 +2188,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -2216,12 +2216,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3389326</t>
+          <t>3388523</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3411220</t>
+          <t>3411024</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2231,12 +2231,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3522489</t>
+          <t>3521805</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3541217</t>
+          <t>3540396</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2266,12 +2266,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6918547</t>
+          <t>6918735</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6948033</t>
+          <t>6947636</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1145</t>
+          <t>1151</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10166</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2718,7 +2718,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7258</t>
+          <t>7148</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2923</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14124</t>
+          <t>13351</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>664634</t>
+          <t>663692</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>673655</t>
+          <t>673649</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665581</t>
+          <t>665691</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1333515</t>
+          <t>1334288</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1344788</t>
+          <t>1344716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2039</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12971</t>
+          <t>13098</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3036,12 +3036,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1759</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13494</t>
+          <t>14550</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4987</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21106</t>
+          <t>21585</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1009460</t>
+          <t>1009333</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1020392</t>
+          <t>1020453</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1029419</t>
+          <t>1028363</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1041154</t>
+          <t>1041826</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2044238</t>
+          <t>2043759</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2060357</t>
+          <t>2060209</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15953</t>
+          <t>14185</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3404,7 +3404,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8937</t>
+          <t>8640</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>3818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18172</t>
+          <t>18468</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>743599</t>
+          <t>745367</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>757018</t>
+          <t>757390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>776074</t>
+          <t>776371</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1526391</t>
+          <t>1526095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1540553</t>
+          <t>1540745</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -3707,12 +3707,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15905</t>
+          <t>15629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3762,7 +3762,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6055</t>
+          <t>6596</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3792,12 +3792,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -3820,12 +3820,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>921662</t>
+          <t>921938</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>933822</t>
+          <t>934486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1033471</t>
+          <t>1033798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1042778</t>
+          <t>1042776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3870,7 +3870,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960431</t>
+          <t>1959002</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975291</t>
+          <t>1974750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3905,12 +3905,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -4050,12 +4050,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15005</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36242</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7265</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23697</t>
+          <t>24768</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27544</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53748</t>
+          <t>55447</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4140,7 +4140,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,8%</t>
         </is>
       </c>
     </row>
@@ -4163,12 +4163,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3358108</t>
+          <t>3356976</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3379345</t>
+          <t>3378462</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3520845</t>
+          <t>3519774</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3537277</t>
+          <t>3537350</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6885144</t>
+          <t>6883445</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6911348</t>
+          <t>6911277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4248,7 +4248,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
